--- a/results/ticketInfo.xlsx
+++ b/results/ticketInfo.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView windowHeight="14680"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="14680"/>
   </bookViews>
   <sheets>
-    <sheet name="机票信息" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="机票信息" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="944">
   <si>
     <t>城市</t>
   </si>
@@ -2682,373 +2669,214 @@
   </si>
   <si>
     <t>9480</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07月03日 06:50</t>
+  </si>
+  <si>
+    <t>07月03日 08:15</t>
+  </si>
+  <si>
+    <t>07月05日 23:10</t>
+  </si>
+  <si>
+    <t>07月06日 01:35</t>
+  </si>
+  <si>
+    <t>约23小时</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07月03日 22:00</t>
+  </si>
+  <si>
+    <t>07月03日 23:50</t>
+  </si>
+  <si>
+    <t>07月05日 11:25</t>
+  </si>
+  <si>
+    <t>07月05日 12:45</t>
+  </si>
+  <si>
+    <t>07月04日 00:35</t>
+  </si>
+  <si>
+    <t>07月05日 10:25</t>
+  </si>
+  <si>
+    <t>07月05日 12:35</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>07月05日 12:40</t>
+  </si>
+  <si>
+    <t>07月05日 07:30</t>
+  </si>
+  <si>
+    <t>07月05日 09:35</t>
+  </si>
+  <si>
+    <t>07月05日 22:20</t>
+  </si>
+  <si>
+    <t>07月06日 00:05</t>
+  </si>
+  <si>
+    <t>07月03日 15:05</t>
+  </si>
+  <si>
+    <t>07月03日 17:05</t>
+  </si>
+  <si>
+    <t>07月05日 13:55</t>
+  </si>
+  <si>
+    <t>07月05日 15:05</t>
+  </si>
+  <si>
+    <t>07月05日 11:45</t>
+  </si>
+  <si>
+    <t>07月05日 12:50</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>07月03日 11:30</t>
+  </si>
+  <si>
+    <t>07月05日 14:45</t>
+  </si>
+  <si>
+    <t>07月05日 17:00</t>
+  </si>
+  <si>
+    <t>07月03日 09:05</t>
+  </si>
+  <si>
+    <t>07月03日 10:40</t>
+  </si>
+  <si>
+    <t>07月05日 23:15</t>
+  </si>
+  <si>
+    <t>07月06日 00:25</t>
+  </si>
+  <si>
+    <t>07月03日 18:40</t>
+  </si>
+  <si>
+    <t>07月04日 00:25</t>
+  </si>
+  <si>
+    <t>07月05日 10:55</t>
+  </si>
+  <si>
+    <t>07月05日 13:25</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>07月03日 06:40</t>
+  </si>
+  <si>
+    <t>07月03日 08:20</t>
+  </si>
+  <si>
+    <t>07月05日 07:35</t>
+  </si>
+  <si>
+    <t>07月05日 08:55</t>
+  </si>
+  <si>
+    <t>07月03日 19:15</t>
+  </si>
+  <si>
+    <t>07月03日 21:25</t>
+  </si>
+  <si>
+    <t>07月05日 22:35</t>
+  </si>
+  <si>
+    <t>07月05日 23:50</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>07月05日 17:15</t>
+  </si>
+  <si>
+    <t>07月05日 18:45</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>23:05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="134"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3056,313 +2884,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3688,17 +3230,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L175"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L220"/>
+  <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="12" width="15" customWidth="1"/>
+    <col min="1" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3736,7 +3275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3774,7 +3313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3812,7 +3351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -3850,7 +3389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -3888,7 +3427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -3926,7 +3465,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -3964,7 +3503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -4002,7 +3541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -4040,7 +3579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -4078,7 +3617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -4116,7 +3655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>81</v>
       </c>
@@ -4154,7 +3693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -4192,7 +3731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -4230,7 +3769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>97</v>
       </c>
@@ -4268,7 +3807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>104</v>
       </c>
@@ -4306,7 +3845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>111</v>
       </c>
@@ -4344,7 +3883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -4382,7 +3921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -4420,7 +3959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>129</v>
       </c>
@@ -4458,7 +3997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>135</v>
       </c>
@@ -4496,7 +4035,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>141</v>
       </c>
@@ -4534,7 +4073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>146</v>
       </c>
@@ -4572,7 +4111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -4610,7 +4149,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>161</v>
       </c>
@@ -4648,7 +4187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>168</v>
       </c>
@@ -4686,7 +4225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>173</v>
       </c>
@@ -4724,7 +4263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>180</v>
       </c>
@@ -4762,7 +4301,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>188</v>
       </c>
@@ -4800,7 +4339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -4838,7 +4377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>199</v>
       </c>
@@ -4876,7 +4415,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>206</v>
       </c>
@@ -4914,7 +4453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>210</v>
       </c>
@@ -4952,7 +4491,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>219</v>
       </c>
@@ -4990,7 +4529,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>227</v>
       </c>
@@ -5028,7 +4567,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>233</v>
       </c>
@@ -5066,7 +4605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>238</v>
       </c>
@@ -5104,7 +4643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>239</v>
       </c>
@@ -5142,7 +4681,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>243</v>
       </c>
@@ -5180,7 +4719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>246</v>
       </c>
@@ -5218,7 +4757,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>252</v>
       </c>
@@ -5256,7 +4795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>258</v>
       </c>
@@ -5294,7 +4833,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>262</v>
       </c>
@@ -5332,7 +4871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>267</v>
       </c>
@@ -5370,7 +4909,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>274</v>
       </c>
@@ -5408,7 +4947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>278</v>
       </c>
@@ -5446,7 +4985,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>282</v>
       </c>
@@ -5484,7 +5023,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>290</v>
       </c>
@@ -5522,7 +5061,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>299</v>
       </c>
@@ -5560,7 +5099,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>306</v>
       </c>
@@ -5598,7 +5137,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>314</v>
       </c>
@@ -5636,7 +5175,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>321</v>
       </c>
@@ -5674,7 +5213,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -5712,7 +5251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>332</v>
       </c>
@@ -5750,7 +5289,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>338</v>
       </c>
@@ -5788,7 +5327,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>343</v>
       </c>
@@ -5826,7 +5365,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>351</v>
       </c>
@@ -5864,7 +5403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>355</v>
       </c>
@@ -5902,7 +5441,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>362</v>
       </c>
@@ -5940,7 +5479,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>366</v>
       </c>
@@ -5978,7 +5517,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>373</v>
       </c>
@@ -6016,7 +5555,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>380</v>
       </c>
@@ -6054,7 +5593,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>385</v>
       </c>
@@ -6092,7 +5631,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>391</v>
       </c>
@@ -6130,7 +5669,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>398</v>
       </c>
@@ -6168,7 +5707,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>404</v>
       </c>
@@ -6206,7 +5745,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>407</v>
       </c>
@@ -6244,7 +5783,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>412</v>
       </c>
@@ -6282,7 +5821,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>418</v>
       </c>
@@ -6320,7 +5859,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>422</v>
       </c>
@@ -6358,7 +5897,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>428</v>
       </c>
@@ -6396,7 +5935,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>435</v>
       </c>
@@ -6434,7 +5973,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>441</v>
       </c>
@@ -6472,7 +6011,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>449</v>
       </c>
@@ -6510,7 +6049,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>451</v>
       </c>
@@ -6548,7 +6087,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>455</v>
       </c>
@@ -6586,7 +6125,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>459</v>
       </c>
@@ -6624,7 +6163,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>466</v>
       </c>
@@ -6662,7 +6201,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>471</v>
       </c>
@@ -6700,7 +6239,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>474</v>
       </c>
@@ -6738,7 +6277,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>481</v>
       </c>
@@ -6776,7 +6315,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>485</v>
       </c>
@@ -6814,7 +6353,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>490</v>
       </c>
@@ -6852,7 +6391,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>494</v>
       </c>
@@ -6890,7 +6429,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>499</v>
       </c>
@@ -6928,7 +6467,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>504</v>
       </c>
@@ -6966,7 +6505,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>507</v>
       </c>
@@ -7004,7 +6543,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>512</v>
       </c>
@@ -7042,7 +6581,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>519</v>
       </c>
@@ -7080,7 +6619,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>525</v>
       </c>
@@ -7118,7 +6657,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>530</v>
       </c>
@@ -7156,7 +6695,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>534</v>
       </c>
@@ -7194,7 +6733,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>538</v>
       </c>
@@ -7232,7 +6771,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>542</v>
       </c>
@@ -7270,7 +6809,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>549</v>
       </c>
@@ -7308,7 +6847,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>555</v>
       </c>
@@ -7346,7 +6885,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>562</v>
       </c>
@@ -7384,7 +6923,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>567</v>
       </c>
@@ -7422,7 +6961,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>573</v>
       </c>
@@ -7460,7 +6999,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>577</v>
       </c>
@@ -7498,7 +7037,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>582</v>
       </c>
@@ -7536,7 +7075,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>587</v>
       </c>
@@ -7574,7 +7113,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>592</v>
       </c>
@@ -7612,7 +7151,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>597</v>
       </c>
@@ -7650,7 +7189,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>603</v>
       </c>
@@ -7688,7 +7227,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>607</v>
       </c>
@@ -7726,7 +7265,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>610</v>
       </c>
@@ -7764,7 +7303,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>615</v>
       </c>
@@ -7802,7 +7341,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>621</v>
       </c>
@@ -7840,7 +7379,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>627</v>
       </c>
@@ -7878,7 +7417,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>632</v>
       </c>
@@ -7916,7 +7455,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>635</v>
       </c>
@@ -7954,7 +7493,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>642</v>
       </c>
@@ -7992,7 +7531,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>648</v>
       </c>
@@ -8030,7 +7569,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>651</v>
       </c>
@@ -8068,7 +7607,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>654</v>
       </c>
@@ -8106,7 +7645,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>659</v>
       </c>
@@ -8144,7 +7683,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>665</v>
       </c>
@@ -8182,7 +7721,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>669</v>
       </c>
@@ -8220,7 +7759,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>676</v>
       </c>
@@ -8258,7 +7797,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>677</v>
       </c>
@@ -8296,7 +7835,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>680</v>
       </c>
@@ -8334,7 +7873,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>684</v>
       </c>
@@ -8372,7 +7911,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>688</v>
       </c>
@@ -8410,7 +7949,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>691</v>
       </c>
@@ -8448,7 +7987,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>694</v>
       </c>
@@ -8486,7 +8025,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>698</v>
       </c>
@@ -8524,7 +8063,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>703</v>
       </c>
@@ -8562,7 +8101,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>706</v>
       </c>
@@ -8600,7 +8139,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>709</v>
       </c>
@@ -8638,7 +8177,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>714</v>
       </c>
@@ -8676,7 +8215,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>716</v>
       </c>
@@ -8714,7 +8253,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>719</v>
       </c>
@@ -8752,7 +8291,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>724</v>
       </c>
@@ -8790,7 +8329,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>728</v>
       </c>
@@ -8828,7 +8367,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>732</v>
       </c>
@@ -8866,7 +8405,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>738</v>
       </c>
@@ -8904,7 +8443,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>742</v>
       </c>
@@ -8942,7 +8481,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>745</v>
       </c>
@@ -8980,7 +8519,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>751</v>
       </c>
@@ -9018,7 +8557,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>755</v>
       </c>
@@ -9056,7 +8595,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>759</v>
       </c>
@@ -9094,7 +8633,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>765</v>
       </c>
@@ -9132,7 +8671,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>769</v>
       </c>
@@ -9170,7 +8709,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>772</v>
       </c>
@@ -9208,7 +8747,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>776</v>
       </c>
@@ -9246,7 +8785,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>781</v>
       </c>
@@ -9284,7 +8823,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>784</v>
       </c>
@@ -9322,7 +8861,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>786</v>
       </c>
@@ -9360,7 +8899,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>789</v>
       </c>
@@ -9398,7 +8937,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>791</v>
       </c>
@@ -9436,7 +8975,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>795</v>
       </c>
@@ -9474,7 +9013,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>798</v>
       </c>
@@ -9512,7 +9051,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>804</v>
       </c>
@@ -9550,7 +9089,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>808</v>
       </c>
@@ -9588,7 +9127,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>811</v>
       </c>
@@ -9626,7 +9165,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>817</v>
       </c>
@@ -9664,7 +9203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>821</v>
       </c>
@@ -9702,7 +9241,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>826</v>
       </c>
@@ -9740,7 +9279,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>830</v>
       </c>
@@ -9778,7 +9317,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>835</v>
       </c>
@@ -9816,7 +9355,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>837</v>
       </c>
@@ -9854,7 +9393,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>840</v>
       </c>
@@ -9892,7 +9431,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>843</v>
       </c>
@@ -9930,7 +9469,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>847</v>
       </c>
@@ -9968,7 +9507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>851</v>
       </c>
@@ -10006,7 +9545,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>856</v>
       </c>
@@ -10044,7 +9583,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>860</v>
       </c>
@@ -10082,7 +9621,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>863</v>
       </c>
@@ -10120,7 +9659,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>864</v>
       </c>
@@ -10158,7 +9697,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>867</v>
       </c>
@@ -10196,7 +9735,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>870</v>
       </c>
@@ -10234,7 +9773,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>874</v>
       </c>
@@ -10272,7 +9811,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>879</v>
       </c>
@@ -10310,7 +9849,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>880</v>
       </c>
@@ -10348,12 +9887,1715 @@
         <v>241</v>
       </c>
     </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>173</v>
+      </c>
+      <c r="B176">
+        <v>688</v>
+      </c>
+      <c r="C176" t="s">
+        <v>885</v>
+      </c>
+      <c r="D176" t="s">
+        <v>886</v>
+      </c>
+      <c r="E176" t="s">
+        <v>887</v>
+      </c>
+      <c r="F176" t="s">
+        <v>888</v>
+      </c>
+      <c r="G176">
+        <v>288</v>
+      </c>
+      <c r="H176" t="s">
+        <v>127</v>
+      </c>
+      <c r="I176" t="s">
+        <v>889</v>
+      </c>
+      <c r="J176" t="s">
+        <v>60</v>
+      </c>
+      <c r="K176">
+        <v>400</v>
+      </c>
+      <c r="L176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>152</v>
+      </c>
+      <c r="B177">
+        <v>1093</v>
+      </c>
+      <c r="C177" t="s">
+        <v>885</v>
+      </c>
+      <c r="D177" t="s">
+        <v>886</v>
+      </c>
+      <c r="E177" t="s">
+        <v>890</v>
+      </c>
+      <c r="F177" t="s">
+        <v>891</v>
+      </c>
+      <c r="G177">
+        <v>345</v>
+      </c>
+      <c r="H177" t="s">
+        <v>214</v>
+      </c>
+      <c r="I177" t="s">
+        <v>892</v>
+      </c>
+      <c r="J177" t="s">
+        <v>893</v>
+      </c>
+      <c r="K177">
+        <v>748</v>
+      </c>
+      <c r="L177" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>12</v>
+      </c>
+      <c r="B178">
+        <v>540</v>
+      </c>
+      <c r="C178" t="s">
+        <v>885</v>
+      </c>
+      <c r="D178" t="s">
+        <v>886</v>
+      </c>
+      <c r="E178" t="s">
+        <v>887</v>
+      </c>
+      <c r="F178" t="s">
+        <v>49</v>
+      </c>
+      <c r="G178">
+        <v>240</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>895</v>
+      </c>
+      <c r="J178" t="s">
+        <v>896</v>
+      </c>
+      <c r="K178">
+        <v>300</v>
+      </c>
+      <c r="L178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>407</v>
+      </c>
+      <c r="B179">
+        <v>1379</v>
+      </c>
+      <c r="C179" t="s">
+        <v>885</v>
+      </c>
+      <c r="D179" t="s">
+        <v>886</v>
+      </c>
+      <c r="E179" t="s">
+        <v>897</v>
+      </c>
+      <c r="F179" t="s">
+        <v>898</v>
+      </c>
+      <c r="G179">
+        <v>695</v>
+      </c>
+      <c r="H179" t="s">
+        <v>803</v>
+      </c>
+      <c r="I179" t="s">
+        <v>899</v>
+      </c>
+      <c r="J179" t="s">
+        <v>900</v>
+      </c>
+      <c r="K179">
+        <v>684</v>
+      </c>
+      <c r="L179" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>698</v>
+      </c>
+      <c r="B180">
+        <v>1869</v>
+      </c>
+      <c r="C180" t="s">
+        <v>885</v>
+      </c>
+      <c r="D180" t="s">
+        <v>886</v>
+      </c>
+      <c r="E180" t="s">
+        <v>897</v>
+      </c>
+      <c r="F180" t="s">
+        <v>901</v>
+      </c>
+      <c r="G180">
+        <v>798</v>
+      </c>
+      <c r="H180" t="s">
+        <v>432</v>
+      </c>
+      <c r="I180" t="s">
+        <v>902</v>
+      </c>
+      <c r="J180" t="s">
+        <v>903</v>
+      </c>
+      <c r="K180">
+        <v>1071</v>
+      </c>
+      <c r="L180" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>173</v>
+      </c>
+      <c r="B181">
+        <v>738</v>
+      </c>
+      <c r="C181" t="s">
+        <v>885</v>
+      </c>
+      <c r="D181" t="s">
+        <v>886</v>
+      </c>
+      <c r="E181" t="s">
+        <v>887</v>
+      </c>
+      <c r="F181" t="s">
+        <v>888</v>
+      </c>
+      <c r="G181">
+        <v>338</v>
+      </c>
+      <c r="H181" t="s">
+        <v>127</v>
+      </c>
+      <c r="I181" t="s">
+        <v>38</v>
+      </c>
+      <c r="J181" t="s">
+        <v>904</v>
+      </c>
+      <c r="K181">
+        <v>400</v>
+      </c>
+      <c r="L181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>173</v>
+      </c>
+      <c r="B182">
+        <v>738</v>
+      </c>
+      <c r="C182" t="s">
+        <v>885</v>
+      </c>
+      <c r="D182" t="s">
+        <v>886</v>
+      </c>
+      <c r="E182" t="s">
+        <v>887</v>
+      </c>
+      <c r="F182" t="s">
+        <v>888</v>
+      </c>
+      <c r="G182">
+        <v>338</v>
+      </c>
+      <c r="H182" t="s">
+        <v>127</v>
+      </c>
+      <c r="I182" t="s">
+        <v>38</v>
+      </c>
+      <c r="J182" t="s">
+        <v>904</v>
+      </c>
+      <c r="K182">
+        <v>400</v>
+      </c>
+      <c r="L182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>152</v>
+      </c>
+      <c r="B183">
+        <v>1090</v>
+      </c>
+      <c r="C183" t="s">
+        <v>885</v>
+      </c>
+      <c r="D183" t="s">
+        <v>886</v>
+      </c>
+      <c r="E183" t="s">
+        <v>890</v>
+      </c>
+      <c r="F183" t="s">
+        <v>891</v>
+      </c>
+      <c r="G183">
+        <v>345</v>
+      </c>
+      <c r="H183" t="s">
+        <v>214</v>
+      </c>
+      <c r="I183" t="s">
+        <v>902</v>
+      </c>
+      <c r="J183" t="s">
+        <v>905</v>
+      </c>
+      <c r="K183">
+        <v>745</v>
+      </c>
+      <c r="L183" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>525</v>
+      </c>
+      <c r="B184">
+        <v>1258</v>
+      </c>
+      <c r="C184" t="s">
+        <v>885</v>
+      </c>
+      <c r="D184" t="s">
+        <v>886</v>
+      </c>
+      <c r="E184" t="s">
+        <v>897</v>
+      </c>
+      <c r="F184" t="s">
+        <v>898</v>
+      </c>
+      <c r="G184">
+        <v>569</v>
+      </c>
+      <c r="H184" t="s">
+        <v>432</v>
+      </c>
+      <c r="I184" t="s">
+        <v>906</v>
+      </c>
+      <c r="J184" t="s">
+        <v>907</v>
+      </c>
+      <c r="K184">
+        <v>689</v>
+      </c>
+      <c r="L184" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185">
+        <v>540</v>
+      </c>
+      <c r="C185" t="s">
+        <v>885</v>
+      </c>
+      <c r="D185" t="s">
+        <v>886</v>
+      </c>
+      <c r="E185" t="s">
+        <v>887</v>
+      </c>
+      <c r="F185" t="s">
+        <v>49</v>
+      </c>
+      <c r="G185">
+        <v>240</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>895</v>
+      </c>
+      <c r="J185" t="s">
+        <v>896</v>
+      </c>
+      <c r="K185">
+        <v>300</v>
+      </c>
+      <c r="L185" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>407</v>
+      </c>
+      <c r="B186">
+        <v>1379</v>
+      </c>
+      <c r="C186" t="s">
+        <v>885</v>
+      </c>
+      <c r="D186" t="s">
+        <v>886</v>
+      </c>
+      <c r="E186" t="s">
+        <v>897</v>
+      </c>
+      <c r="F186" t="s">
+        <v>898</v>
+      </c>
+      <c r="G186">
+        <v>695</v>
+      </c>
+      <c r="H186" t="s">
+        <v>803</v>
+      </c>
+      <c r="I186" t="s">
+        <v>899</v>
+      </c>
+      <c r="J186" t="s">
+        <v>900</v>
+      </c>
+      <c r="K186">
+        <v>684</v>
+      </c>
+      <c r="L186" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>698</v>
+      </c>
+      <c r="B187">
+        <v>1870</v>
+      </c>
+      <c r="C187" t="s">
+        <v>885</v>
+      </c>
+      <c r="D187" t="s">
+        <v>886</v>
+      </c>
+      <c r="E187" t="s">
+        <v>897</v>
+      </c>
+      <c r="F187" t="s">
+        <v>901</v>
+      </c>
+      <c r="G187">
+        <v>798</v>
+      </c>
+      <c r="H187" t="s">
+        <v>432</v>
+      </c>
+      <c r="I187" t="s">
+        <v>902</v>
+      </c>
+      <c r="J187" t="s">
+        <v>903</v>
+      </c>
+      <c r="K187">
+        <v>1072</v>
+      </c>
+      <c r="L187" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>30</v>
+      </c>
+      <c r="B188">
+        <v>1743</v>
+      </c>
+      <c r="C188" t="s">
+        <v>885</v>
+      </c>
+      <c r="D188" t="s">
+        <v>886</v>
+      </c>
+      <c r="E188" t="s">
+        <v>897</v>
+      </c>
+      <c r="F188" t="s">
+        <v>901</v>
+      </c>
+      <c r="G188">
+        <v>718</v>
+      </c>
+      <c r="H188" t="s">
+        <v>214</v>
+      </c>
+      <c r="I188" t="s">
+        <v>908</v>
+      </c>
+      <c r="J188" t="s">
+        <v>909</v>
+      </c>
+      <c r="K188">
+        <v>1025</v>
+      </c>
+      <c r="L188" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>306</v>
+      </c>
+      <c r="B189">
+        <v>996</v>
+      </c>
+      <c r="C189" t="s">
+        <v>885</v>
+      </c>
+      <c r="D189" t="s">
+        <v>886</v>
+      </c>
+      <c r="E189" t="s">
+        <v>910</v>
+      </c>
+      <c r="F189" t="s">
+        <v>911</v>
+      </c>
+      <c r="G189">
+        <v>500</v>
+      </c>
+      <c r="H189" t="s">
+        <v>184</v>
+      </c>
+      <c r="I189" t="s">
+        <v>912</v>
+      </c>
+      <c r="J189" t="s">
+        <v>913</v>
+      </c>
+      <c r="K189">
+        <v>496</v>
+      </c>
+      <c r="L189" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>373</v>
+      </c>
+      <c r="B190">
+        <v>937</v>
+      </c>
+      <c r="C190" t="s">
+        <v>885</v>
+      </c>
+      <c r="D190" t="s">
+        <v>886</v>
+      </c>
+      <c r="E190" t="s">
+        <v>897</v>
+      </c>
+      <c r="F190" t="s">
+        <v>898</v>
+      </c>
+      <c r="G190">
+        <v>420</v>
+      </c>
+      <c r="H190" t="s">
+        <v>586</v>
+      </c>
+      <c r="I190" t="s">
+        <v>914</v>
+      </c>
+      <c r="J190" t="s">
+        <v>915</v>
+      </c>
+      <c r="K190">
+        <v>517</v>
+      </c>
+      <c r="L190" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>141</v>
+      </c>
+      <c r="B191">
+        <v>810</v>
+      </c>
+      <c r="C191" t="s">
+        <v>885</v>
+      </c>
+      <c r="D191" t="s">
+        <v>886</v>
+      </c>
+      <c r="E191" t="s">
+        <v>38</v>
+      </c>
+      <c r="F191" t="s">
+        <v>916</v>
+      </c>
+      <c r="G191">
+        <v>340</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>887</v>
+      </c>
+      <c r="J191" t="s">
+        <v>20</v>
+      </c>
+      <c r="K191">
+        <v>470</v>
+      </c>
+      <c r="L191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>706</v>
+      </c>
+      <c r="B192">
+        <v>1784</v>
+      </c>
+      <c r="C192" t="s">
+        <v>885</v>
+      </c>
+      <c r="D192" t="s">
+        <v>886</v>
+      </c>
+      <c r="E192" t="s">
+        <v>890</v>
+      </c>
+      <c r="F192" t="s">
+        <v>917</v>
+      </c>
+      <c r="G192">
+        <v>966</v>
+      </c>
+      <c r="H192" t="s">
+        <v>586</v>
+      </c>
+      <c r="I192" t="s">
+        <v>918</v>
+      </c>
+      <c r="J192" t="s">
+        <v>919</v>
+      </c>
+      <c r="K192">
+        <v>818</v>
+      </c>
+      <c r="L192" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>243</v>
+      </c>
+      <c r="B193">
+        <v>980</v>
+      </c>
+      <c r="C193" t="s">
+        <v>885</v>
+      </c>
+      <c r="D193" t="s">
+        <v>886</v>
+      </c>
+      <c r="E193" t="s">
+        <v>128</v>
+      </c>
+      <c r="F193" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193">
+        <v>490</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>95</v>
+      </c>
+      <c r="J193" t="s">
+        <v>98</v>
+      </c>
+      <c r="K193">
+        <v>490</v>
+      </c>
+      <c r="L193" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>781</v>
+      </c>
+      <c r="B194">
+        <v>1287</v>
+      </c>
+      <c r="C194" t="s">
+        <v>885</v>
+      </c>
+      <c r="D194" t="s">
+        <v>886</v>
+      </c>
+      <c r="E194" t="s">
+        <v>920</v>
+      </c>
+      <c r="F194" t="s">
+        <v>921</v>
+      </c>
+      <c r="G194">
+        <v>650</v>
+      </c>
+      <c r="H194" t="s">
+        <v>214</v>
+      </c>
+      <c r="I194" t="s">
+        <v>922</v>
+      </c>
+      <c r="J194" t="s">
+        <v>923</v>
+      </c>
+      <c r="K194">
+        <v>637</v>
+      </c>
+      <c r="L194" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>111</v>
+      </c>
+      <c r="B195">
+        <v>1038</v>
+      </c>
+      <c r="C195" t="s">
+        <v>885</v>
+      </c>
+      <c r="D195" t="s">
+        <v>886</v>
+      </c>
+      <c r="E195" t="s">
+        <v>228</v>
+      </c>
+      <c r="F195" t="s">
+        <v>381</v>
+      </c>
+      <c r="G195">
+        <v>489</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>106</v>
+      </c>
+      <c r="J195" t="s">
+        <v>41</v>
+      </c>
+      <c r="K195">
+        <v>549</v>
+      </c>
+      <c r="L195" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>688</v>
+      </c>
+      <c r="B196">
+        <v>2025</v>
+      </c>
+      <c r="C196" t="s">
+        <v>885</v>
+      </c>
+      <c r="D196" t="s">
+        <v>886</v>
+      </c>
+      <c r="E196" t="s">
+        <v>924</v>
+      </c>
+      <c r="F196" t="s">
+        <v>925</v>
+      </c>
+      <c r="G196">
+        <v>948</v>
+      </c>
+      <c r="H196" t="s">
+        <v>286</v>
+      </c>
+      <c r="I196" t="s">
+        <v>926</v>
+      </c>
+      <c r="J196" t="s">
+        <v>927</v>
+      </c>
+      <c r="K196">
+        <v>1077</v>
+      </c>
+      <c r="L196" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>64</v>
+      </c>
+      <c r="B197">
+        <v>1020</v>
+      </c>
+      <c r="C197" t="s">
+        <v>885</v>
+      </c>
+      <c r="D197" t="s">
+        <v>886</v>
+      </c>
+      <c r="E197" t="s">
+        <v>928</v>
+      </c>
+      <c r="F197" t="s">
+        <v>122</v>
+      </c>
+      <c r="G197">
+        <v>500</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>929</v>
+      </c>
+      <c r="J197" t="s">
+        <v>263</v>
+      </c>
+      <c r="K197">
+        <v>520</v>
+      </c>
+      <c r="L197" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>58</v>
+      </c>
+      <c r="B198">
+        <v>1181</v>
+      </c>
+      <c r="C198" t="s">
+        <v>885</v>
+      </c>
+      <c r="D198" t="s">
+        <v>886</v>
+      </c>
+      <c r="E198" t="s">
+        <v>930</v>
+      </c>
+      <c r="F198" t="s">
+        <v>931</v>
+      </c>
+      <c r="G198">
+        <v>589</v>
+      </c>
+      <c r="H198" t="s">
+        <v>156</v>
+      </c>
+      <c r="I198" t="s">
+        <v>932</v>
+      </c>
+      <c r="J198" t="s">
+        <v>933</v>
+      </c>
+      <c r="K198">
+        <v>592</v>
+      </c>
+      <c r="L198" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>412</v>
+      </c>
+      <c r="B199">
+        <v>1497</v>
+      </c>
+      <c r="C199" t="s">
+        <v>885</v>
+      </c>
+      <c r="D199" t="s">
+        <v>886</v>
+      </c>
+      <c r="E199" t="s">
+        <v>934</v>
+      </c>
+      <c r="F199" t="s">
+        <v>935</v>
+      </c>
+      <c r="G199">
+        <v>830</v>
+      </c>
+      <c r="H199" t="s">
+        <v>586</v>
+      </c>
+      <c r="I199" t="s">
+        <v>936</v>
+      </c>
+      <c r="J199" t="s">
+        <v>937</v>
+      </c>
+      <c r="K199">
+        <v>667</v>
+      </c>
+      <c r="L199" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>173</v>
+      </c>
+      <c r="B200">
+        <v>738</v>
+      </c>
+      <c r="C200" t="s">
+        <v>885</v>
+      </c>
+      <c r="D200" t="s">
+        <v>886</v>
+      </c>
+      <c r="E200" t="s">
+        <v>887</v>
+      </c>
+      <c r="F200" t="s">
+        <v>888</v>
+      </c>
+      <c r="G200">
+        <v>338</v>
+      </c>
+      <c r="H200" t="s">
+        <v>127</v>
+      </c>
+      <c r="I200" t="s">
+        <v>38</v>
+      </c>
+      <c r="J200" t="s">
+        <v>904</v>
+      </c>
+      <c r="K200">
+        <v>400</v>
+      </c>
+      <c r="L200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>152</v>
+      </c>
+      <c r="B201">
+        <v>1091</v>
+      </c>
+      <c r="C201" t="s">
+        <v>885</v>
+      </c>
+      <c r="D201" t="s">
+        <v>886</v>
+      </c>
+      <c r="E201" t="s">
+        <v>890</v>
+      </c>
+      <c r="F201" t="s">
+        <v>891</v>
+      </c>
+      <c r="G201">
+        <v>345</v>
+      </c>
+      <c r="H201" t="s">
+        <v>214</v>
+      </c>
+      <c r="I201" t="s">
+        <v>902</v>
+      </c>
+      <c r="J201" t="s">
+        <v>905</v>
+      </c>
+      <c r="K201">
+        <v>746</v>
+      </c>
+      <c r="L201" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>525</v>
+      </c>
+      <c r="B202">
+        <v>1258</v>
+      </c>
+      <c r="C202" t="s">
+        <v>885</v>
+      </c>
+      <c r="D202" t="s">
+        <v>886</v>
+      </c>
+      <c r="E202" t="s">
+        <v>897</v>
+      </c>
+      <c r="F202" t="s">
+        <v>898</v>
+      </c>
+      <c r="G202">
+        <v>569</v>
+      </c>
+      <c r="H202" t="s">
+        <v>432</v>
+      </c>
+      <c r="I202" t="s">
+        <v>906</v>
+      </c>
+      <c r="J202" t="s">
+        <v>907</v>
+      </c>
+      <c r="K202">
+        <v>689</v>
+      </c>
+      <c r="L202" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>51</v>
+      </c>
+      <c r="B203">
+        <v>690</v>
+      </c>
+      <c r="C203" t="s">
+        <v>885</v>
+      </c>
+      <c r="D203" t="s">
+        <v>886</v>
+      </c>
+      <c r="E203" t="s">
+        <v>528</v>
+      </c>
+      <c r="F203" t="s">
+        <v>144</v>
+      </c>
+      <c r="G203">
+        <v>320</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>938</v>
+      </c>
+      <c r="J203" t="s">
+        <v>330</v>
+      </c>
+      <c r="K203">
+        <v>370</v>
+      </c>
+      <c r="L203" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>173</v>
+      </c>
+      <c r="B204">
+        <v>738</v>
+      </c>
+      <c r="C204" t="s">
+        <v>885</v>
+      </c>
+      <c r="D204" t="s">
+        <v>886</v>
+      </c>
+      <c r="E204" t="s">
+        <v>887</v>
+      </c>
+      <c r="F204" t="s">
+        <v>888</v>
+      </c>
+      <c r="G204">
+        <v>338</v>
+      </c>
+      <c r="H204" t="s">
+        <v>127</v>
+      </c>
+      <c r="I204" t="s">
+        <v>38</v>
+      </c>
+      <c r="J204" t="s">
+        <v>904</v>
+      </c>
+      <c r="K204">
+        <v>400</v>
+      </c>
+      <c r="L204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>152</v>
+      </c>
+      <c r="B205">
+        <v>1091</v>
+      </c>
+      <c r="C205" t="s">
+        <v>885</v>
+      </c>
+      <c r="D205" t="s">
+        <v>886</v>
+      </c>
+      <c r="E205" t="s">
+        <v>890</v>
+      </c>
+      <c r="F205" t="s">
+        <v>891</v>
+      </c>
+      <c r="G205">
+        <v>345</v>
+      </c>
+      <c r="H205" t="s">
+        <v>214</v>
+      </c>
+      <c r="I205" t="s">
+        <v>902</v>
+      </c>
+      <c r="J205" t="s">
+        <v>905</v>
+      </c>
+      <c r="K205">
+        <v>746</v>
+      </c>
+      <c r="L205" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>173</v>
+      </c>
+      <c r="B206">
+        <v>738</v>
+      </c>
+      <c r="C206" t="s">
+        <v>885</v>
+      </c>
+      <c r="D206" t="s">
+        <v>886</v>
+      </c>
+      <c r="E206" t="s">
+        <v>887</v>
+      </c>
+      <c r="F206" t="s">
+        <v>888</v>
+      </c>
+      <c r="G206">
+        <v>338</v>
+      </c>
+      <c r="H206" t="s">
+        <v>127</v>
+      </c>
+      <c r="I206" t="s">
+        <v>38</v>
+      </c>
+      <c r="J206" t="s">
+        <v>904</v>
+      </c>
+      <c r="K206">
+        <v>400</v>
+      </c>
+      <c r="L206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>152</v>
+      </c>
+      <c r="B207">
+        <v>1091</v>
+      </c>
+      <c r="C207" t="s">
+        <v>885</v>
+      </c>
+      <c r="D207" t="s">
+        <v>886</v>
+      </c>
+      <c r="E207" t="s">
+        <v>890</v>
+      </c>
+      <c r="F207" t="s">
+        <v>891</v>
+      </c>
+      <c r="G207">
+        <v>345</v>
+      </c>
+      <c r="H207" t="s">
+        <v>214</v>
+      </c>
+      <c r="I207" t="s">
+        <v>902</v>
+      </c>
+      <c r="J207" t="s">
+        <v>905</v>
+      </c>
+      <c r="K207">
+        <v>746</v>
+      </c>
+      <c r="L207" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>525</v>
+      </c>
+      <c r="B208">
+        <v>1208</v>
+      </c>
+      <c r="C208" t="s">
+        <v>885</v>
+      </c>
+      <c r="D208" t="s">
+        <v>886</v>
+      </c>
+      <c r="E208" t="s">
+        <v>897</v>
+      </c>
+      <c r="F208" t="s">
+        <v>898</v>
+      </c>
+      <c r="G208">
+        <v>569</v>
+      </c>
+      <c r="H208" t="s">
+        <v>432</v>
+      </c>
+      <c r="I208" t="s">
+        <v>906</v>
+      </c>
+      <c r="J208" t="s">
+        <v>907</v>
+      </c>
+      <c r="K208">
+        <v>639</v>
+      </c>
+      <c r="L208" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209">
+        <v>500</v>
+      </c>
+      <c r="C209" t="s">
+        <v>885</v>
+      </c>
+      <c r="D209" t="s">
+        <v>886</v>
+      </c>
+      <c r="E209" t="s">
+        <v>887</v>
+      </c>
+      <c r="F209" t="s">
+        <v>49</v>
+      </c>
+      <c r="G209">
+        <v>200</v>
+      </c>
+      <c r="H209" t="s">
+        <v>18</v>
+      </c>
+      <c r="I209" t="s">
+        <v>895</v>
+      </c>
+      <c r="J209" t="s">
+        <v>896</v>
+      </c>
+      <c r="K209">
+        <v>300</v>
+      </c>
+      <c r="L209" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>407</v>
+      </c>
+      <c r="B210">
+        <v>1380</v>
+      </c>
+      <c r="C210" t="s">
+        <v>885</v>
+      </c>
+      <c r="D210" t="s">
+        <v>886</v>
+      </c>
+      <c r="E210" t="s">
+        <v>897</v>
+      </c>
+      <c r="F210" t="s">
+        <v>898</v>
+      </c>
+      <c r="G210">
+        <v>696</v>
+      </c>
+      <c r="H210" t="s">
+        <v>803</v>
+      </c>
+      <c r="I210" t="s">
+        <v>899</v>
+      </c>
+      <c r="J210" t="s">
+        <v>900</v>
+      </c>
+      <c r="K210">
+        <v>684</v>
+      </c>
+      <c r="L210" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>698</v>
+      </c>
+      <c r="B211">
+        <v>1725</v>
+      </c>
+      <c r="C211" t="s">
+        <v>885</v>
+      </c>
+      <c r="D211" t="s">
+        <v>886</v>
+      </c>
+      <c r="E211" t="s">
+        <v>897</v>
+      </c>
+      <c r="F211" t="s">
+        <v>901</v>
+      </c>
+      <c r="G211">
+        <v>798</v>
+      </c>
+      <c r="H211" t="s">
+        <v>432</v>
+      </c>
+      <c r="I211" t="s">
+        <v>902</v>
+      </c>
+      <c r="J211" t="s">
+        <v>903</v>
+      </c>
+      <c r="K211">
+        <v>927</v>
+      </c>
+      <c r="L211" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>30</v>
+      </c>
+      <c r="B212">
+        <v>1742</v>
+      </c>
+      <c r="C212" t="s">
+        <v>885</v>
+      </c>
+      <c r="D212" t="s">
+        <v>886</v>
+      </c>
+      <c r="E212" t="s">
+        <v>897</v>
+      </c>
+      <c r="F212" t="s">
+        <v>901</v>
+      </c>
+      <c r="G212">
+        <v>718</v>
+      </c>
+      <c r="H212" t="s">
+        <v>214</v>
+      </c>
+      <c r="I212" t="s">
+        <v>908</v>
+      </c>
+      <c r="J212" t="s">
+        <v>909</v>
+      </c>
+      <c r="K212">
+        <v>1024</v>
+      </c>
+      <c r="L212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>306</v>
+      </c>
+      <c r="B213">
+        <v>996</v>
+      </c>
+      <c r="C213" t="s">
+        <v>885</v>
+      </c>
+      <c r="D213" t="s">
+        <v>886</v>
+      </c>
+      <c r="E213" t="s">
+        <v>910</v>
+      </c>
+      <c r="F213" t="s">
+        <v>911</v>
+      </c>
+      <c r="G213">
+        <v>500</v>
+      </c>
+      <c r="H213" t="s">
+        <v>184</v>
+      </c>
+      <c r="I213" t="s">
+        <v>912</v>
+      </c>
+      <c r="J213" t="s">
+        <v>913</v>
+      </c>
+      <c r="K213">
+        <v>496</v>
+      </c>
+      <c r="L213" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>373</v>
+      </c>
+      <c r="B214">
+        <v>937</v>
+      </c>
+      <c r="C214" t="s">
+        <v>885</v>
+      </c>
+      <c r="D214" t="s">
+        <v>886</v>
+      </c>
+      <c r="E214" t="s">
+        <v>897</v>
+      </c>
+      <c r="F214" t="s">
+        <v>898</v>
+      </c>
+      <c r="G214">
+        <v>420</v>
+      </c>
+      <c r="H214" t="s">
+        <v>586</v>
+      </c>
+      <c r="I214" t="s">
+        <v>914</v>
+      </c>
+      <c r="J214" t="s">
+        <v>915</v>
+      </c>
+      <c r="K214">
+        <v>517</v>
+      </c>
+      <c r="L214" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>141</v>
+      </c>
+      <c r="B215">
+        <v>810</v>
+      </c>
+      <c r="C215" t="s">
+        <v>885</v>
+      </c>
+      <c r="D215" t="s">
+        <v>886</v>
+      </c>
+      <c r="E215" t="s">
+        <v>38</v>
+      </c>
+      <c r="F215" t="s">
+        <v>916</v>
+      </c>
+      <c r="G215">
+        <v>340</v>
+      </c>
+      <c r="H215" t="s">
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>887</v>
+      </c>
+      <c r="J215" t="s">
+        <v>20</v>
+      </c>
+      <c r="K215">
+        <v>470</v>
+      </c>
+      <c r="L215" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>706</v>
+      </c>
+      <c r="B216">
+        <v>1784</v>
+      </c>
+      <c r="C216" t="s">
+        <v>885</v>
+      </c>
+      <c r="D216" t="s">
+        <v>886</v>
+      </c>
+      <c r="E216" t="s">
+        <v>890</v>
+      </c>
+      <c r="F216" t="s">
+        <v>917</v>
+      </c>
+      <c r="G216">
+        <v>966</v>
+      </c>
+      <c r="H216" t="s">
+        <v>586</v>
+      </c>
+      <c r="I216" t="s">
+        <v>918</v>
+      </c>
+      <c r="J216" t="s">
+        <v>919</v>
+      </c>
+      <c r="K216">
+        <v>818</v>
+      </c>
+      <c r="L216" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>694</v>
+      </c>
+      <c r="B217">
+        <v>1340</v>
+      </c>
+      <c r="C217" t="s">
+        <v>885</v>
+      </c>
+      <c r="D217" t="s">
+        <v>886</v>
+      </c>
+      <c r="E217" t="s">
+        <v>920</v>
+      </c>
+      <c r="F217" t="s">
+        <v>921</v>
+      </c>
+      <c r="G217">
+        <v>690</v>
+      </c>
+      <c r="H217" t="s">
+        <v>156</v>
+      </c>
+      <c r="I217" t="s">
+        <v>939</v>
+      </c>
+      <c r="J217" t="s">
+        <v>940</v>
+      </c>
+      <c r="K217">
+        <v>650</v>
+      </c>
+      <c r="L217" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>51</v>
+      </c>
+      <c r="B218">
+        <v>760</v>
+      </c>
+      <c r="C218" t="s">
+        <v>941</v>
+      </c>
+      <c r="D218" t="s">
+        <v>942</v>
+      </c>
+      <c r="E218" t="s">
+        <v>45</v>
+      </c>
+      <c r="F218" t="s">
+        <v>943</v>
+      </c>
+      <c r="G218">
+        <v>390</v>
+      </c>
+      <c r="H218" t="s">
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>938</v>
+      </c>
+      <c r="J218" t="s">
+        <v>330</v>
+      </c>
+      <c r="K218">
+        <v>370</v>
+      </c>
+      <c r="L218" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>51</v>
+      </c>
+      <c r="B219">
+        <v>760</v>
+      </c>
+      <c r="C219" t="s">
+        <v>941</v>
+      </c>
+      <c r="D219" t="s">
+        <v>942</v>
+      </c>
+      <c r="E219" t="s">
+        <v>45</v>
+      </c>
+      <c r="F219" t="s">
+        <v>943</v>
+      </c>
+      <c r="G219">
+        <v>390</v>
+      </c>
+      <c r="H219" t="s">
+        <v>18</v>
+      </c>
+      <c r="I219" t="s">
+        <v>938</v>
+      </c>
+      <c r="J219" t="s">
+        <v>330</v>
+      </c>
+      <c r="K219">
+        <v>370</v>
+      </c>
+      <c r="L219" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>173</v>
+      </c>
+      <c r="B220">
+        <v>528</v>
+      </c>
+      <c r="C220" t="s">
+        <v>941</v>
+      </c>
+      <c r="D220" t="s">
+        <v>942</v>
+      </c>
+      <c r="E220" t="s">
+        <v>887</v>
+      </c>
+      <c r="F220" t="s">
+        <v>888</v>
+      </c>
+      <c r="G220">
+        <v>288</v>
+      </c>
+      <c r="I220" t="s">
+        <v>38</v>
+      </c>
+      <c r="J220" t="s">
+        <v>904</v>
+      </c>
+      <c r="K220">
+        <v>240</v>
+      </c>
+      <c r="L220" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:L175">
-    <sortCondition ref="B2:B175"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
-  <headerFooter/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>